--- a/mcp/Formic_Acid_Quote.xlsx
+++ b/mcp/Formic_Acid_Quote.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Formic Acid extrapure AR, 98%</t>
+          <t>Formic acid, 85%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1038,37 +1038,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Part A</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>100 ml</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>500.0</v>
+        <v>220.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.18</v>
       </c>
       <c r="I15" t="n">
-        <v>410.00000000000006</v>
+        <v>180.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>410.00000000000006</v>
+        <v>180.4</v>
       </c>
       <c r="L15" t="n">
         <v>0.18</v>
       </c>
       <c r="M15" t="n">
-        <v>73.80000000000001</v>
+        <v>32.472</v>
       </c>
       <c r="N15" t="n">
-        <v>483.80000000000007</v>
+        <v>212.872</v>
       </c>
     </row>
     <row r="16">
@@ -1092,37 +1092,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>100 ml</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>220.0</v>
+        <v>407.0</v>
       </c>
       <c r="H16" t="n">
         <v>0.18</v>
       </c>
       <c r="I16" t="n">
-        <v>180.4</v>
+        <v>333.74</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>180.4</v>
+        <v>333.74</v>
       </c>
       <c r="L16" t="n">
         <v>0.18</v>
       </c>
       <c r="M16" t="n">
-        <v>32.472</v>
+        <v>60.0732</v>
       </c>
       <c r="N16" t="n">
-        <v>212.872</v>
+        <v>393.8132</v>
       </c>
     </row>
     <row r="17">
@@ -1146,37 +1146,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>2.5 L</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>407.0</v>
+        <v>1320.0</v>
       </c>
       <c r="H17" t="n">
         <v>0.18</v>
       </c>
       <c r="I17" t="n">
-        <v>333.74</v>
+        <v>1082.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>333.74</v>
+        <v>1082.4</v>
       </c>
       <c r="L17" t="n">
         <v>0.18</v>
       </c>
       <c r="M17" t="n">
-        <v>60.0732</v>
+        <v>194.83200000000002</v>
       </c>
       <c r="N17" t="n">
-        <v>393.8132</v>
+        <v>1277.2320000000002</v>
       </c>
     </row>
     <row r="18">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Formic acid, 85%</t>
+          <t>Formic acid, 98%</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1200,37 +1200,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.5 L</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1320.0</v>
+        <v>770.0</v>
       </c>
       <c r="H18" t="n">
         <v>0.18</v>
       </c>
       <c r="I18" t="n">
-        <v>1082.4</v>
+        <v>631.4000000000001</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1082.4</v>
+        <v>631.4000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0.18</v>
       </c>
       <c r="M18" t="n">
-        <v>194.83200000000002</v>
+        <v>113.65200000000002</v>
       </c>
       <c r="N18" t="n">
-        <v>1277.2320000000002</v>
+        <v>745.0520000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1254,37 +1254,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>2.5 L</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>770.0</v>
+        <v>3220.0</v>
       </c>
       <c r="H19" t="n">
         <v>0.18</v>
       </c>
       <c r="I19" t="n">
-        <v>631.4000000000001</v>
+        <v>2640.4</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>631.4000000000001</v>
+        <v>2640.4</v>
       </c>
       <c r="L19" t="n">
         <v>0.18</v>
       </c>
       <c r="M19" t="n">
-        <v>113.65200000000002</v>
+        <v>475.272</v>
       </c>
       <c r="N19" t="n">
-        <v>745.0520000000001</v>
+        <v>3115.672</v>
       </c>
     </row>
     <row r="20">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Formic acid, 98%</t>
+          <t>Formic acid (purity not specified)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1308,37 +1308,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.5 L</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3220.0</v>
+        <v>770.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.18</v>
       </c>
       <c r="I20" t="n">
-        <v>2640.4</v>
+        <v>631.4000000000001</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2640.4</v>
+        <v>631.4000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>0.18</v>
       </c>
       <c r="M20" t="n">
-        <v>475.272</v>
+        <v>113.65200000000002</v>
       </c>
       <c r="N20" t="n">
-        <v>3115.672</v>
+        <v>745.0520000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Formic acid</t>
+          <t>Formic acid (purity not specified)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1362,37 +1362,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>2.5 L</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>770.0</v>
+        <v>3080.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.18</v>
       </c>
       <c r="I21" t="n">
-        <v>631.4000000000001</v>
+        <v>2525.6000000000004</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>631.4000000000001</v>
+        <v>2525.6000000000004</v>
       </c>
       <c r="L21" t="n">
         <v>0.18</v>
       </c>
       <c r="M21" t="n">
-        <v>113.65200000000002</v>
+        <v>454.60800000000006</v>
       </c>
       <c r="N21" t="n">
-        <v>745.0520000000001</v>
+        <v>2980.2080000000005</v>
       </c>
     </row>
     <row r="22">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Formic acid</t>
+          <t>Formic Acid extrapure AR, 98%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1416,37 +1416,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Part A</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.5 L</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3080.0</v>
+        <v>500.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.18</v>
       </c>
       <c r="I22" t="n">
-        <v>2525.6000000000004</v>
+        <v>410.00000000000006</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2525.6000000000004</v>
+        <v>410.00000000000006</v>
       </c>
       <c r="L22" t="n">
         <v>0.18</v>
       </c>
       <c r="M22" t="n">
-        <v>454.60800000000006</v>
+        <v>73.80000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>2980.2080000000005</v>
+        <v>483.80000000000007</v>
       </c>
     </row>
     <row r="23">
